--- a/InputData/fuels/BCTR/BAU Carbon Tax Rate.xlsx
+++ b/InputData/fuels/BCTR/BAU Carbon Tax Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/fuels/BCTR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B2C274-9851-CD41-9968-2CEF4044BC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558D2923-3EC8-7D4B-9B80-F296B8A59212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,15 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>BCTR BAU Carbon Tax Rate</t>
   </si>
   <si>
     <t>Source:</t>
-  </si>
-  <si>
-    <t>none needed</t>
   </si>
   <si>
     <t>Notes</t>
@@ -80,12 +77,27 @@
   <si>
     <t>geoengineering sector (uses industry sector rate)</t>
   </si>
+  <si>
+    <t>The Staits Times</t>
+  </si>
+  <si>
+    <t>https://www.straitstimes.com/asia/se-asia/indonesia-launches-carbon-trading-under-push-to-tame-coal</t>
+  </si>
+  <si>
+    <t>2024 Rupiah to USD</t>
+  </si>
+  <si>
+    <t>ETS (Rupiah per tonne)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,6 +123,14 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -146,17 +166,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -170,6 +197,109 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="header-logo-component" descr="The Straits Times logo">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC64787C-3A6E-8675-546D-092CCB52AF98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="660400" y="355600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="header-logo-component" descr="The Straits Times logo">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA769134-7A4F-4E06-8F0D-DF95EB339AC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="660400" y="355600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -370,47 +500,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1000"/>
+  <dimension ref="A1:D1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="5">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2">
+        <v>69600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+    <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
+    <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>6.2997267759562806E-5</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1395,9 +1552,15 @@
     <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{61535445-2388-FF47-9592-552731E2E0C6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1406,16 +1569,16 @@
   <sheetPr>
     <tabColor rgb="FF2F5496"/>
   </sheetPr>
-  <dimension ref="A1:AG1000"/>
+  <dimension ref="A1:BA1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="33" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1">
         <v>2019</v>
@@ -1513,822 +1676,1362 @@
       <c r="AG1" s="1">
         <v>2050</v>
       </c>
+      <c r="AH1" s="1">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="1">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="1">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="1">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="1">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="1">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="1">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="1">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="1">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="1">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="1">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="1">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="1">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="1">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="1">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="1">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="1">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="1">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2">
+        <v>0</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0</v>
+      </c>
+      <c r="X2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2">
-        <v>0</v>
-      </c>
-      <c r="S2" s="2">
-        <v>0</v>
-      </c>
-      <c r="T2" s="2">
-        <v>0</v>
-      </c>
-      <c r="U2" s="2">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2">
-        <v>0</v>
-      </c>
-      <c r="W2" s="2">
-        <v>0</v>
-      </c>
-      <c r="X2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="2">
-        <v>0</v>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="I3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="J3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="K3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="L3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="M3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="N3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="R3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="S3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="T3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="U3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="V3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="W3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="X3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AE3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AF3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AG3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AH3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AI3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AJ3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AK3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AL3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AM3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AN3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AO3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AP3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AQ3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AR3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AS3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AT3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AU3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AV3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AW3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AX3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AY3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AZ3" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="BA3" s="2">
+        <v>4.5</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="G3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="H3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="I3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="J3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="K3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="L3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="M3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="N3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="P3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="R3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="S3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="T3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="U3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="V3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="W3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="X3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="Z3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="AA3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="AC3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="AD3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="AE3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="AF3" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="AG3" s="2">
-        <v>4.5</v>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
-        <v>0</v>
-      </c>
-      <c r="T4" s="2">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2">
-        <v>0</v>
-      </c>
-      <c r="W4" s="2">
-        <v>0</v>
-      </c>
-      <c r="X4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="2">
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0</v>
+      </c>
+      <c r="W5" s="2">
+        <v>0</v>
+      </c>
+      <c r="X5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2">
-        <v>0</v>
-      </c>
-      <c r="X5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="2">
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2">
-        <v>0</v>
-      </c>
-      <c r="U6" s="2">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2">
-        <v>0</v>
-      </c>
-      <c r="W6" s="2">
-        <v>0</v>
-      </c>
-      <c r="X6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="2">
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2">
-        <v>0</v>
-      </c>
-      <c r="W7" s="2">
-        <v>0</v>
-      </c>
-      <c r="X7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="2">
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+    <row r="9" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2">
-        <v>0</v>
-      </c>
-      <c r="U8" s="2">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2">
-        <v>0</v>
-      </c>
-      <c r="W8" s="2">
-        <v>0</v>
-      </c>
-      <c r="X8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="2">
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2">
-        <v>0</v>
-      </c>
-      <c r="U9" s="2">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2">
-        <v>0</v>
-      </c>
-      <c r="W9" s="2">
-        <v>0</v>
-      </c>
-      <c r="X9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/InputData/fuels/BCTR/BAU Carbon Tax Rate.xlsx
+++ b/InputData/fuels/BCTR/BAU Carbon Tax Rate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/fuels/BCTR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558D2923-3EC8-7D4B-9B80-F296B8A59212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3B1C30-C018-9441-9AC3-6E6D0DB65481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,18 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>BCTR BAU Carbon Tax Rate</t>
   </si>
   <si>
     <t>Source:</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>There is no carbon tax in Indonesia</t>
   </si>
   <si>
     <t>Unit: $/metric ton CO2e</t>
@@ -78,26 +72,35 @@
     <t>geoengineering sector (uses industry sector rate)</t>
   </si>
   <si>
-    <t>The Staits Times</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>https://www.straitstimes.com/asia/se-asia/indonesia-launches-carbon-trading-under-push-to-tame-coal</t>
+    <t>ETS ($ per tonne)</t>
   </si>
   <si>
-    <t>2024 Rupiah to USD</t>
+    <t>$2024 to $2012</t>
   </si>
   <si>
-    <t>ETS (Rupiah per tonne)</t>
+    <t>Unlocking Indonesia’s renewable energy investment potential</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Institute for Financial and energy Economics</t>
+  </si>
+  <si>
+    <t>https://ieefa.org/resources/unlocking-indonesias-renewable-energy-investment-potential</t>
+  </si>
+  <si>
+    <t>Conversion</t>
+  </si>
+  <si>
+    <t>https://www.in2013dollars.com/us/inflation/2024?endYear=2012&amp;amount=1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,6 +134,20 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -170,7 +187,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -179,8 +196,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -297,6 +321,50 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D81C6F1-7119-3083-5594-9EEEDE8AFAE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2730500"/>
+          <a:ext cx="8064500" cy="8509000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -500,10 +568,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1002"/>
+  <dimension ref="A1:D1003"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="26" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -516,56 +585,67 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="5">
-        <v>2024</v>
+      <c r="B4" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="7" t="s">
-        <v>14</v>
+      <c r="A5" s="2"/>
+      <c r="B5" s="5">
+        <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2">
-        <v>69600</v>
-      </c>
     </row>
+    <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>3</v>
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7">
+        <v>0.61</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6">
-        <v>6.2997267759562806E-5</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="A13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="9">
+        <v>0.73</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1554,9 +1634,10 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{61535445-2388-FF47-9592-552731E2E0C6}"/>
+    <hyperlink ref="B12" r:id="rId1" xr:uid="{366178F5-601D-A342-A593-FE276EBF8979}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -1578,7 +1659,7 @@
   <sheetData>
     <row r="1" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1">
         <v>2019</v>
@@ -1739,7 +1820,7 @@
     </row>
     <row r="2" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -1900,168 +1981,219 @@
     </row>
     <row r="3" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
         <v>0</v>
       </c>
       <c r="C3" s="2">
+        <f>B3</f>
         <v>0</v>
       </c>
       <c r="D3" s="2">
+        <f t="shared" ref="D3:BA3" si="0">C3</f>
         <v>0</v>
       </c>
       <c r="E3" s="2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>4.5</v>
+        <f>About!B10*About!A14</f>
+        <v>0.44529999999999997</v>
       </c>
       <c r="I3" s="2">
-        <v>4.5</v>
+        <f>H3</f>
+        <v>0.44529999999999997</v>
       </c>
       <c r="J3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="K3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="L3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="M3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="N3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="O3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="P3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="Q3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="R3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="S3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="T3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="U3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="V3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="W3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="X3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="Y3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="Z3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AA3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AB3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AC3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AD3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AE3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AF3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AG3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AH3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AI3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AJ3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AK3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AL3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AM3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AN3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AO3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AP3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AQ3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AR3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AS3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AT3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AU3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AV3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AW3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AX3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AY3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="AZ3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
       <c r="BA3" s="2">
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>0.44529999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
@@ -2222,7 +2354,7 @@
     </row>
     <row r="5" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
@@ -2383,7 +2515,7 @@
     </row>
     <row r="6" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2">
         <v>0</v>
@@ -2544,7 +2676,7 @@
     </row>
     <row r="7" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
@@ -2705,7 +2837,7 @@
     </row>
     <row r="8" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2">
         <v>0</v>
@@ -2866,7 +2998,7 @@
     </row>
     <row r="9" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2">
         <v>0</v>
@@ -4019,5 +4151,8 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
+  <ignoredErrors>
+    <ignoredError sqref="H3" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>